--- a/Result/profitability/6624.xlsx
+++ b/Result/profitability/6624.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM41"/>
+  <dimension ref="A1:AM42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5637,6 +5637,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>6624</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>99</v>
+      </c>
+      <c r="D42" t="n">
+        <v>88</v>
+      </c>
+      <c r="E42" t="n">
+        <v>11</v>
+      </c>
+      <c r="F42" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-4.41%</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.21125</v>
+      </c>
+      <c r="N42" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W42" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-12.35</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-0.522198731501057</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-0.6428571428571428</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-12.73</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>-0.5297544735746983</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK42" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
